--- a/yuk-manifest.xlsx
+++ b/yuk-manifest.xlsx
@@ -557,13 +557,13 @@
         <v/>
       </c>
       <c r="T2" t="str">
-        <v>Yo'q</v>
+        <v>Ha</v>
       </c>
       <c r="U2" t="str">
-        <v/>
-      </c>
-      <c r="V2" t="str">
-        <v/>
+        <v>2026-07-17</v>
+      </c>
+      <c r="V2">
+        <v>2000000</v>
       </c>
       <c r="W2" t="str">
         <v>2026-07-15T09:16:07.439Z</v>

--- a/yuk-manifest.xlsx
+++ b/yuk-manifest.xlsx
@@ -500,28 +500,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B2" t="str">
-        <v>qizil</v>
+        <v>sariq</v>
       </c>
       <c r="C2" t="str">
         <v>Shkaf</v>
       </c>
       <c r="D2" t="str">
-        <v>Leyla</v>
+        <v>leylaaa</v>
       </c>
       <c r="E2" t="str">
-        <v>lipa</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Zör shavad</v>
+        <v>akuratniy shavad</v>
       </c>
       <c r="H2" t="str">
-        <v>Mulyon</v>
+        <v>ravonak</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="M2" t="str">
-        <v>933468632</v>
+        <v>7776451314</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -557,16 +557,16 @@
         <v/>
       </c>
       <c r="T2" t="str">
-        <v>Ha</v>
+        <v>Yo'q</v>
       </c>
       <c r="U2" t="str">
-        <v>2026-07-17</v>
-      </c>
-      <c r="V2">
-        <v>2000000</v>
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
       </c>
       <c r="W2" t="str">
-        <v>2026-07-15T09:16:07.439Z</v>
+        <v>2026-07-18T07:12:15.748Z</v>
       </c>
     </row>
   </sheetData>
